--- a/SPCX.xlsx
+++ b/SPCX.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11BA3EA1-2502-4CFE-B6A4-AE295C45F230}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94588EDB-69E7-473B-9540-8CE0CFE9481E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" xr2:uid="{F03B917A-17F4-4DB6-93D6-77129ABA2B7A}"/>
   </bookViews>
@@ -492,7 +492,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.0;\(#,##0.0\)"/>
     <numFmt numFmtId="166" formatCode="#,##0.00;\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -525,12 +525,6 @@
       <sz val="10"/>
       <color theme="10"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -866,9 +860,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -906,7 +900,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1012,7 +1006,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1154,7 +1148,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1188,13 +1182,17 @@
       <c r="J2" t="s">
         <v>21</v>
       </c>
-      <c r="K2" s="5"/>
+      <c r="K2" s="5">
+        <v>135</v>
+      </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="J3" t="s">
         <v>22</v>
       </c>
-      <c r="K3" s="5"/>
+      <c r="K3" s="5">
+        <v>555.6</v>
+      </c>
       <c r="L3" s="4" t="s">
         <v>38</v>
       </c>
@@ -1203,7 +1201,10 @@
       <c r="J4" t="s">
         <v>23</v>
       </c>
-      <c r="K4" s="5"/>
+      <c r="K4" s="5">
+        <f>+K2*K3</f>
+        <v>75006</v>
+      </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
@@ -2033,7 +2034,7 @@
         <v>-0.284393063583815</v>
       </c>
       <c r="L32" s="9" t="e">
-        <f t="shared" ref="L32:N32" si="17">+L11/K11-1</f>
+        <f t="shared" ref="L32:M32" si="17">+L11/K11-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M32" s="9">
@@ -2153,7 +2154,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="L36" s="9">
-        <f t="shared" ref="L36:N36" si="20">+L16/L14</f>
+        <f t="shared" ref="L36:M36" si="20">+L16/L14</f>
         <v>0.41176470588235292</v>
       </c>
       <c r="M36" s="9">
@@ -2202,7 +2203,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="L37" s="9">
-        <f t="shared" ref="L37:N37" si="22">+L21/L14</f>
+        <f t="shared" ref="L37:M37" si="22">+L21/L14</f>
         <v>-0.33744103205930492</v>
       </c>
       <c r="M37" s="9">
@@ -2251,7 +2252,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="L38" s="9">
-        <f t="shared" ref="L38:N38" si="24">+L26/L25</f>
+        <f t="shared" ref="L38:M38" si="24">+L26/L25</f>
         <v>7.2730915648166694E-2</v>
       </c>
       <c r="M38" s="9">
@@ -2591,7 +2592,7 @@
         <v>75</v>
       </c>
       <c r="L68" s="5">
-        <f t="shared" ref="L68:N68" si="28">+L27</f>
+        <f t="shared" ref="L68:M68" si="28">+L27</f>
         <v>-4628</v>
       </c>
       <c r="M68" s="5">

--- a/SPCX.xlsx
+++ b/SPCX.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94588EDB-69E7-473B-9540-8CE0CFE9481E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42D0B618-3816-4A9E-B565-B71823AD3926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" xr2:uid="{F03B917A-17F4-4DB6-93D6-77129ABA2B7A}"/>
+    <workbookView xWindow="225" yWindow="2730" windowWidth="38175" windowHeight="15240" xr2:uid="{F03B917A-17F4-4DB6-93D6-77129ABA2B7A}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="142">
   <si>
     <t>Space Exploration Technologies Crop</t>
   </si>
@@ -69,15 +69,6 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>IPO planned for June 2026</t>
-  </si>
-  <si>
-    <t>Want to raise 75$ billion at 1.5$ trillion valuation</t>
-  </si>
-  <si>
-    <t>would be the biggest IPO of all time</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cursor Acquistion </t>
   </si>
   <si>
@@ -481,6 +472,18 @@
   </si>
   <si>
     <t>S1-Filing</t>
+  </si>
+  <si>
+    <t>IPO on 12.06.2026</t>
+  </si>
+  <si>
+    <t>Raised 75$ b. -&gt; biggest IPO in history</t>
+  </si>
+  <si>
+    <t>Opened at 135$, closed at 166,8$</t>
+  </si>
+  <si>
+    <t>2.3 Trillion market cap after day 1</t>
   </si>
 </sst>
 </file>
@@ -1164,7 +1167,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB11B4F1-9D8F-4CDB-86E2-C2AE46F8989E}">
-  <dimension ref="A1:L37"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.85546875" customWidth="1"/>
@@ -1180,89 +1183,92 @@
         <v>1</v>
       </c>
       <c r="J2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K2" s="5">
-        <v>135</v>
+        <v>166.83</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="J3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K3" s="5">
-        <v>555.6</v>
+        <v>13800</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="J4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K4" s="5">
         <f>+K2*K3</f>
-        <v>75006</v>
+        <v>2302254</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="K5" s="5">
         <v>24747</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J6" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K6" s="5">
         <f>928+21968</f>
         <v>22896</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J7" t="s">
-        <v>26</v>
-      </c>
-      <c r="K7" s="5"/>
+        <v>23</v>
+      </c>
+      <c r="K7" s="5">
+        <f>+K4-K5+K6</f>
+        <v>2300403</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="J9" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="K9" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="J10" t="s">
+        <v>24</v>
+      </c>
+      <c r="K10" t="s">
         <v>27</v>
-      </c>
-      <c r="K10" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
@@ -1270,182 +1276,187 @@
         <v>2</v>
       </c>
       <c r="J11" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K11" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
-        <v>3</v>
+        <v>138</v>
       </c>
       <c r="J12" t="s">
+        <v>55</v>
+      </c>
+      <c r="K12" t="s">
         <v>58</v>
-      </c>
-      <c r="K12" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
-        <v>4</v>
+        <v>139</v>
       </c>
       <c r="J13" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="K13" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B15" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B18" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H18" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B19" t="s">
+        <v>4</v>
+      </c>
+      <c r="H19" s="5">
+        <v>-675</v>
+      </c>
+      <c r="I19">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B20" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B16" s="2" t="s">
+      <c r="H20" s="5">
+        <v>-21</v>
+      </c>
+      <c r="I20">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="H21" s="5">
+        <v>1</v>
+      </c>
+      <c r="I21">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B23" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B24" t="s">
+        <v>6</v>
+      </c>
+      <c r="H24" s="5">
+        <v>4423</v>
+      </c>
+      <c r="I24">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B25" t="s">
+        <v>7</v>
+      </c>
+      <c r="H25" s="5">
+        <v>2006</v>
+      </c>
+      <c r="I25">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="H26" s="5">
+        <v>469</v>
+      </c>
+      <c r="I26">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B29" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="H16" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" t="s">
-        <v>7</v>
-      </c>
-      <c r="H17" s="5">
-        <v>-675</v>
-      </c>
-      <c r="I17">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B18" t="s">
-        <v>8</v>
-      </c>
-      <c r="H18" s="5">
-        <v>-21</v>
-      </c>
-      <c r="I18">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="H19" s="5">
-        <v>1</v>
-      </c>
-      <c r="I19">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B21" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B22" t="s">
-        <v>9</v>
-      </c>
-      <c r="H22" s="5">
-        <v>4423</v>
-      </c>
-      <c r="I22">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B23" t="s">
-        <v>10</v>
-      </c>
-      <c r="H23" s="5">
-        <v>2006</v>
-      </c>
-      <c r="I23">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="H24" s="5">
-        <v>469</v>
-      </c>
-      <c r="I24">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B27" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" t="s">
-        <v>15</v>
-      </c>
-      <c r="H28" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B29" t="s">
-        <v>18</v>
-      </c>
-      <c r="H29" s="5">
-        <v>-6355</v>
-      </c>
-      <c r="I29">
-        <v>2025</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B30" t="s">
-        <v>16</v>
-      </c>
-      <c r="H30" s="5">
-        <v>-1561</v>
-      </c>
-      <c r="I30">
-        <v>2024</v>
+        <v>12</v>
+      </c>
+      <c r="H30" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H31" s="5">
-        <v>-3973</v>
+        <v>-6355</v>
       </c>
       <c r="I31">
-        <v>2023</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B32" t="s">
-        <v>19</v>
-      </c>
-      <c r="H32" s="5"/>
-    </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+      <c r="H32" s="5">
+        <v>-1561</v>
+      </c>
+      <c r="I32">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.2">
+        <v>14</v>
+      </c>
+      <c r="H33" s="5">
+        <v>-3973</v>
+      </c>
+      <c r="I33">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B34" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+      <c r="H34" s="5"/>
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B35" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B36" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B37" t="s">
-        <v>57</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B38" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B39" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -1466,47 +1477,47 @@
   <sheetData>
     <row r="1" spans="1:14" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:14" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="I2" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="J2" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="H2" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>42</v>
-      </c>
       <c r="L2" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C3" s="5">
         <v>450</v>
@@ -1526,7 +1537,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C4" s="5">
         <v>36</v>
@@ -1546,7 +1557,7 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C5" s="5">
         <v>2</v>
@@ -1566,7 +1577,7 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C6" s="5">
         <f>+C4+C5</f>
@@ -1615,7 +1626,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C7" s="6">
         <v>5</v>
@@ -1642,7 +1653,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C8" s="5">
         <v>86</v>
@@ -1662,7 +1673,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C9" s="6">
         <v>0.3</v>
@@ -1689,7 +1700,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C11" s="5">
         <v>865</v>
@@ -1709,7 +1720,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C12" s="5">
         <v>2475</v>
@@ -1729,7 +1740,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C13" s="5">
         <v>727</v>
@@ -1749,7 +1760,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C14" s="7">
         <f t="shared" ref="C14" si="2">+SUM(C11:C13)</f>
@@ -1798,7 +1809,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="L15" s="5">
         <v>6110</v>
@@ -1812,7 +1823,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="L16" s="5">
         <f t="shared" ref="L16:M16" si="11">+L14-L15</f>
@@ -1829,7 +1840,7 @@
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="L17" s="5">
         <v>2105</v>
@@ -1843,7 +1854,7 @@
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="L18" s="5">
         <v>1665</v>
@@ -1857,7 +1868,7 @@
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="L19" s="5">
         <v>237</v>
@@ -1871,7 +1882,7 @@
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="L20" s="5">
         <v>3775</v>
@@ -1885,7 +1896,7 @@
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="L21" s="5">
         <f t="shared" ref="L21:M21" si="12">+L16-SUM(L17:L20)</f>
@@ -1902,7 +1913,7 @@
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="L22" s="5">
         <v>1693</v>
@@ -1916,7 +1927,7 @@
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="L23" s="5">
         <v>249</v>
@@ -1930,7 +1941,7 @@
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="L24" s="5">
         <v>-42</v>
@@ -1944,7 +1955,7 @@
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B25" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="L25" s="5">
         <f t="shared" ref="L25:M25" si="13">+L21-L22+L23+L24</f>
@@ -1961,7 +1972,7 @@
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="L26" s="5">
         <v>-363</v>
@@ -1975,7 +1986,7 @@
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="L27" s="5">
         <f t="shared" ref="L27:M27" si="14">+L25-L26</f>
@@ -1992,7 +2003,7 @@
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B29" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="K29" s="8" t="e">
         <f t="shared" ref="K29:M29" si="15">+K27/K30</f>
@@ -2013,7 +2024,7 @@
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B30" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="L30" s="5">
         <v>2759</v>
@@ -2027,7 +2038,7 @@
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G32" s="11">
         <f t="shared" ref="G32:G34" si="16">+G11/C11-1</f>
@@ -2048,7 +2059,7 @@
     </row>
     <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G33" s="11">
         <f t="shared" si="16"/>
@@ -2069,7 +2080,7 @@
     </row>
     <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B34" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G34" s="11">
         <f t="shared" si="16"/>
@@ -2090,7 +2101,7 @@
     </row>
     <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B35" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C35" s="7"/>
       <c r="D35" s="7"/>
@@ -2119,7 +2130,7 @@
     </row>
     <row r="36" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B36" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C36" s="9">
         <f t="shared" ref="C36:J36" si="19">+C16/C14</f>
@@ -2168,7 +2179,7 @@
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C37" s="9">
         <f t="shared" ref="C37:J37" si="21">+C21/C14</f>
@@ -2217,7 +2228,7 @@
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B38" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C38" s="9" t="e">
         <f t="shared" ref="C38:J38" si="23">+C26/C25</f>
@@ -2266,7 +2277,7 @@
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B40" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="M40" s="5">
         <v>11385</v>
@@ -2277,7 +2288,7 @@
     </row>
     <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B41" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="M41" s="5">
         <v>800</v>
@@ -2288,7 +2299,7 @@
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B42" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="M42" s="5">
         <v>1052</v>
@@ -2299,7 +2310,7 @@
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B43" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="M43" s="5">
         <v>2003</v>
@@ -2310,7 +2321,7 @@
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B44" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="M44" s="5">
         <v>868</v>
@@ -2321,7 +2332,7 @@
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B45" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M45" s="5">
         <f t="shared" ref="M45" si="25">+SUM(M40:M44)</f>
@@ -2334,7 +2345,7 @@
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B46" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="M46" s="5">
         <v>21147</v>
@@ -2345,7 +2356,7 @@
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B47" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M47" s="5">
         <v>1686</v>
@@ -2356,7 +2367,7 @@
     </row>
     <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B48" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="M48" s="5">
         <v>2211</v>
@@ -2367,7 +2378,7 @@
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B49" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="M49" s="5">
         <v>1749</v>
@@ -2378,7 +2389,7 @@
     </row>
     <row r="50" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B50" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M50" s="5">
         <v>11129</v>
@@ -2389,7 +2400,7 @@
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B51" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="M51" s="5">
         <v>696</v>
@@ -2400,7 +2411,7 @@
     </row>
     <row r="52" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B52" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="M52" s="5">
         <v>2336</v>
@@ -2411,7 +2422,7 @@
     </row>
     <row r="53" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B53" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="M53" s="5">
         <f t="shared" ref="M53" si="26">+SUM(M46:M52)</f>
@@ -2424,7 +2435,7 @@
     </row>
     <row r="54" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B54" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="M54" s="7">
         <f t="shared" ref="M54" si="27">+M53+M45</f>
@@ -2437,7 +2448,7 @@
     </row>
     <row r="55" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B55" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="M55" s="5">
         <v>4413</v>
@@ -2448,7 +2459,7 @@
     </row>
     <row r="56" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B56" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="M56" s="5">
         <v>5498</v>
@@ -2459,7 +2470,7 @@
     </row>
     <row r="57" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B57" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="M57" s="5">
         <v>372</v>
@@ -2470,7 +2481,7 @@
     </row>
     <row r="58" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B58" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="M58" s="5">
         <v>1508</v>
@@ -2481,7 +2492,7 @@
     </row>
     <row r="59" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B59" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="M59" s="5">
         <f>+SUM(M55:M58)</f>
@@ -2494,7 +2505,7 @@
     </row>
     <row r="60" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B60" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="M60" s="5">
         <v>4681</v>
@@ -2505,7 +2516,7 @@
     </row>
     <row r="61" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B61" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="M61" s="5">
         <v>13421</v>
@@ -2516,7 +2527,7 @@
     </row>
     <row r="62" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B62" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="M62" s="5">
         <v>1365</v>
@@ -2527,7 +2538,7 @@
     </row>
     <row r="63" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B63" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="M63" s="5">
         <f>+SUM(M60:M62)</f>
@@ -2540,7 +2551,7 @@
     </row>
     <row r="64" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B64" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C64" s="7"/>
       <c r="D64" s="7"/>
@@ -2563,7 +2574,7 @@
     </row>
     <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B65" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="M65" s="5">
         <f>20941+4863</f>
@@ -2576,7 +2587,7 @@
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B66" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="M66" s="7">
         <f>+M64+M65</f>
@@ -2589,7 +2600,7 @@
     </row>
     <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B68" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="L68" s="5">
         <f t="shared" ref="L68:M68" si="28">+L27</f>
@@ -2606,7 +2617,7 @@
     </row>
     <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B69" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="L69" s="5">
         <v>2635</v>
@@ -2620,7 +2631,7 @@
     </row>
     <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B70" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="L70" s="5">
         <v>679</v>
@@ -2634,7 +2645,7 @@
     </row>
     <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B71" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="L71" s="5">
         <v>-409</v>
@@ -2648,7 +2659,7 @@
     </row>
     <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B72" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="L72" s="5">
         <f>3775+36+212</f>
@@ -2665,7 +2676,7 @@
     </row>
     <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B73" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="L73" s="5">
         <v>214</v>
@@ -2679,7 +2690,7 @@
     </row>
     <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B74" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="L74" s="5">
         <v>345</v>
@@ -2693,7 +2704,7 @@
     </row>
     <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B75" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="L75" s="5">
         <v>-72</v>
@@ -2707,7 +2718,7 @@
     </row>
     <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B76" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="L76" s="5">
         <v>41</v>
@@ -2721,7 +2732,7 @@
     </row>
     <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B77" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="L77" s="5">
         <v>220</v>
@@ -2735,7 +2746,7 @@
     </row>
     <row r="78" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B78" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="L78" s="5">
         <v>1695</v>
@@ -2749,7 +2760,7 @@
     </row>
     <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="L79" s="5">
         <v>-15</v>
@@ -2763,7 +2774,7 @@
     </row>
     <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B80" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="L80" s="5">
         <v>-208</v>
@@ -2777,7 +2788,7 @@
     </row>
     <row r="81" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B81" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="L81" s="5">
         <f t="shared" ref="L81:M81" si="29">+SUM(L74:L80)</f>
@@ -2794,7 +2805,7 @@
     </row>
     <row r="82" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B82" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C82" s="7"/>
       <c r="D82" s="7"/>
@@ -2820,7 +2831,7 @@
     </row>
     <row r="83" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B83" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="L83" s="5">
         <v>-4415</v>
@@ -2834,7 +2845,7 @@
     </row>
     <row r="84" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B84" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="L84" s="5">
         <v>-3535</v>
@@ -2848,7 +2859,7 @@
     </row>
     <row r="85" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B85" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="L85" s="5">
         <f>2731+333</f>
@@ -2865,7 +2876,7 @@
     </row>
     <row r="86" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B86" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="L86" s="5">
         <v>0</v>
@@ -2879,7 +2890,7 @@
     </row>
     <row r="87" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B87" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="L87" s="5">
         <v>19</v>
@@ -2894,7 +2905,7 @@
     </row>
     <row r="88" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B88" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="L88" s="7">
         <f t="shared" ref="L88:M88" si="31">+SUM(L83:L87)</f>
@@ -2911,7 +2922,7 @@
     </row>
     <row r="89" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B89" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="L89" s="5">
         <v>0</v>
@@ -2925,7 +2936,7 @@
     </row>
     <row r="90" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B90" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="L90" s="5">
         <v>0</v>
@@ -2940,7 +2951,7 @@
     </row>
     <row r="91" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B91" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="L91" s="5">
         <v>-112</v>
@@ -2955,7 +2966,7 @@
     </row>
     <row r="92" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B92" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="L92" s="5">
         <v>774</v>
@@ -2969,7 +2980,7 @@
     </row>
     <row r="93" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B93" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="L93" s="5">
         <v>141</v>
@@ -2983,7 +2994,7 @@
     </row>
     <row r="94" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B94" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L94" s="5">
         <v>-170</v>
@@ -2997,7 +3008,7 @@
     </row>
     <row r="95" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B95" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="L95" s="5">
         <v>-211</v>
@@ -3011,7 +3022,7 @@
     </row>
     <row r="96" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B96" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C96" s="7"/>
       <c r="D96" s="7"/>
@@ -3037,7 +3048,7 @@
     </row>
     <row r="97" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B97" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="L97" s="5">
         <v>-2</v>
@@ -3051,7 +3062,7 @@
     </row>
     <row r="98" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B98" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="L98" s="5">
         <f t="shared" ref="L98:M98" si="32">+L96+L88+L82+L97</f>
@@ -3068,7 +3079,7 @@
     </row>
     <row r="100" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B100" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="L100" s="5">
         <f>+L101-L98</f>
@@ -3084,7 +3095,7 @@
     </row>
     <row r="101" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B101" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="L101" s="5">
         <f>+M100</f>

--- a/SPCX.xlsx
+++ b/SPCX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42D0B618-3816-4A9E-B565-B71823AD3926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C88932DC-3B2A-4653-9CFC-02CC4A2E6351}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="2730" windowWidth="38175" windowHeight="15240" xr2:uid="{F03B917A-17F4-4DB6-93D6-77129ABA2B7A}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19305" windowHeight="20985" activeTab="1" xr2:uid="{F03B917A-17F4-4DB6-93D6-77129ABA2B7A}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -1186,7 +1186,7 @@
         <v>18</v>
       </c>
       <c r="K2" s="5">
-        <v>166.83</v>
+        <v>115.64</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
@@ -1194,10 +1194,11 @@
         <v>19</v>
       </c>
       <c r="K3" s="5">
-        <v>13800</v>
+        <f>7696.293669+5485.486276</f>
+        <v>13181.779944999998</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
@@ -1206,7 +1207,7 @@
       </c>
       <c r="K4" s="5">
         <f>+K2*K3</f>
-        <v>2302254</v>
+        <v>1524341.0328397998</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
@@ -1217,10 +1218,11 @@
         <v>21</v>
       </c>
       <c r="K5" s="5">
-        <v>24747</v>
+        <f>93522+6487</f>
+        <v>100009</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
@@ -1231,11 +1233,11 @@
         <v>22</v>
       </c>
       <c r="K6" s="5">
-        <f>928+21968</f>
-        <v>22896</v>
+        <f>36839+2525</f>
+        <v>39364</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
@@ -1247,7 +1249,7 @@
       </c>
       <c r="K7" s="5">
         <f>+K4-K5+K6</f>
-        <v>2300403</v>
+        <v>1463696.0328397998</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
@@ -1705,8 +1707,14 @@
       <c r="C11" s="5">
         <v>865</v>
       </c>
+      <c r="D11" s="5">
+        <v>746</v>
+      </c>
       <c r="G11" s="5">
         <v>619</v>
+      </c>
+      <c r="H11" s="5">
+        <v>962</v>
       </c>
       <c r="L11" s="5">
         <v>3557</v>
@@ -1725,8 +1733,14 @@
       <c r="C12" s="5">
         <v>2475</v>
       </c>
+      <c r="D12" s="5">
+        <v>2588</v>
+      </c>
       <c r="G12" s="5">
         <v>3257</v>
+      </c>
+      <c r="H12" s="5">
+        <v>4291</v>
       </c>
       <c r="L12" s="5">
         <v>3869</v>
@@ -1745,8 +1759,14 @@
       <c r="C13" s="5">
         <v>727</v>
       </c>
+      <c r="D13" s="5">
+        <v>737</v>
+      </c>
       <c r="G13" s="5">
         <v>818</v>
+      </c>
+      <c r="H13" s="5">
+        <v>2561</v>
       </c>
       <c r="L13" s="5">
         <v>2961</v>
@@ -1767,39 +1787,37 @@
         <v>4067</v>
       </c>
       <c r="D14" s="7">
-        <f t="shared" ref="D14" si="3">+SUM(D11:D13)</f>
+        <v>4071</v>
+      </c>
+      <c r="E14" s="7">
+        <f t="shared" ref="E14" si="3">+SUM(E11:E13)</f>
         <v>0</v>
       </c>
-      <c r="E14" s="7">
-        <f t="shared" ref="E14" si="4">+SUM(E11:E13)</f>
+      <c r="F14" s="7">
+        <f t="shared" ref="F14" si="4">+SUM(F11:F13)</f>
         <v>0</v>
       </c>
-      <c r="F14" s="7">
-        <f t="shared" ref="F14" si="5">+SUM(F11:F13)</f>
+      <c r="G14" s="7">
+        <f t="shared" ref="G14" si="5">+SUM(G11:G13)</f>
+        <v>4694</v>
+      </c>
+      <c r="H14" s="7">
+        <v>7814</v>
+      </c>
+      <c r="I14" s="7">
+        <f t="shared" ref="I14" si="6">+SUM(I11:I13)</f>
         <v>0</v>
       </c>
-      <c r="G14" s="7">
-        <f t="shared" ref="G14" si="6">+SUM(G11:G13)</f>
-        <v>4694</v>
-      </c>
-      <c r="H14" s="7">
-        <f t="shared" ref="H14" si="7">+SUM(H11:H13)</f>
+      <c r="J14" s="7">
+        <f t="shared" ref="J14" si="7">+SUM(J11:J13)</f>
         <v>0</v>
       </c>
-      <c r="I14" s="7">
-        <f t="shared" ref="I14" si="8">+SUM(I11:I13)</f>
-        <v>0</v>
-      </c>
-      <c r="J14" s="7">
-        <f t="shared" ref="J14" si="9">+SUM(J11:J13)</f>
-        <v>0</v>
-      </c>
       <c r="L14" s="7">
-        <f t="shared" ref="L14:M14" si="10">+SUM(L11:L13)</f>
+        <f t="shared" ref="L14:M14" si="8">+SUM(L11:L13)</f>
         <v>10387</v>
       </c>
       <c r="M14" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>14015</v>
       </c>
       <c r="N14" s="7">
@@ -1811,6 +1829,20 @@
       <c r="B15" t="s">
         <v>60</v>
       </c>
+      <c r="C15" s="5">
+        <f>4244-D15</f>
+        <v>1962</v>
+      </c>
+      <c r="D15" s="5">
+        <v>2282</v>
+      </c>
+      <c r="G15" s="5">
+        <f>5883-H15</f>
+        <v>2388</v>
+      </c>
+      <c r="H15" s="5">
+        <v>3495</v>
+      </c>
       <c r="L15" s="5">
         <v>6110</v>
       </c>
@@ -1825,12 +1857,36 @@
       <c r="B16" t="s">
         <v>61</v>
       </c>
+      <c r="C16" s="5">
+        <f>+C14-C15</f>
+        <v>2105</v>
+      </c>
+      <c r="D16" s="5">
+        <f t="shared" ref="D16:H16" si="9">+D14-D15</f>
+        <v>1789</v>
+      </c>
+      <c r="E16" s="5">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="5">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="5">
+        <f t="shared" si="9"/>
+        <v>2306</v>
+      </c>
+      <c r="H16" s="5">
+        <f t="shared" si="9"/>
+        <v>4319</v>
+      </c>
       <c r="L16" s="5">
-        <f t="shared" ref="L16:M16" si="11">+L14-L15</f>
+        <f t="shared" ref="L16:M16" si="10">+L14-L15</f>
         <v>4277</v>
       </c>
       <c r="M16" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>6019</v>
       </c>
       <c r="N16" s="5">
@@ -1842,6 +1898,20 @@
       <c r="B17" t="s">
         <v>62</v>
       </c>
+      <c r="C17" s="5">
+        <f>3515-D17</f>
+        <v>1557</v>
+      </c>
+      <c r="D17" s="5">
+        <v>1958</v>
+      </c>
+      <c r="G17" s="5">
+        <f>7062-H17</f>
+        <v>3514</v>
+      </c>
+      <c r="H17" s="5">
+        <v>3548</v>
+      </c>
       <c r="L17" s="5">
         <v>2105</v>
       </c>
@@ -1856,6 +1926,20 @@
       <c r="B18" t="s">
         <v>63</v>
       </c>
+      <c r="C18" s="5">
+        <f>1099-D18</f>
+        <v>493</v>
+      </c>
+      <c r="D18" s="5">
+        <v>606</v>
+      </c>
+      <c r="G18" s="5">
+        <f>1658-H18</f>
+        <v>746</v>
+      </c>
+      <c r="H18" s="5">
+        <v>912</v>
+      </c>
       <c r="L18" s="5">
         <v>1665</v>
       </c>
@@ -1870,6 +1954,20 @@
       <c r="B19" t="s">
         <v>64</v>
       </c>
+      <c r="C19" s="5">
+        <f>194-D19</f>
+        <v>4</v>
+      </c>
+      <c r="D19" s="5">
+        <v>190</v>
+      </c>
+      <c r="G19" s="5">
+        <f>-9-H19</f>
+        <v>-11</v>
+      </c>
+      <c r="H19" s="5">
+        <v>2</v>
+      </c>
       <c r="L19" s="5">
         <v>237</v>
       </c>
@@ -1884,6 +1982,19 @@
       <c r="B20" t="s">
         <v>65</v>
       </c>
+      <c r="C20" s="5">
+        <f>29-D20</f>
+        <v>24</v>
+      </c>
+      <c r="D20" s="5">
+        <v>5</v>
+      </c>
+      <c r="G20" s="5">
+        <v>0</v>
+      </c>
+      <c r="H20" s="5">
+        <v>0</v>
+      </c>
       <c r="L20" s="5">
         <v>3775</v>
       </c>
@@ -1898,6 +2009,38 @@
       <c r="B21" t="s">
         <v>66</v>
       </c>
+      <c r="C21" s="5">
+        <f t="shared" ref="C21:J21" si="11">+C16-SUM(C17:C20)</f>
+        <v>27</v>
+      </c>
+      <c r="D21" s="5">
+        <f t="shared" si="11"/>
+        <v>-970</v>
+      </c>
+      <c r="E21" s="5">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="F21" s="5">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="G21" s="5">
+        <f t="shared" si="11"/>
+        <v>-1943</v>
+      </c>
+      <c r="H21" s="5">
+        <f t="shared" si="11"/>
+        <v>-143</v>
+      </c>
+      <c r="I21" s="5">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J21" s="5">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="L21" s="5">
         <f t="shared" ref="L21:M21" si="12">+L16-SUM(L17:L20)</f>
         <v>-3505</v>
@@ -1915,6 +2058,20 @@
       <c r="B22" t="s">
         <v>67</v>
       </c>
+      <c r="C22" s="5">
+        <f>858-D22</f>
+        <v>447</v>
+      </c>
+      <c r="D22" s="5">
+        <v>411</v>
+      </c>
+      <c r="G22" s="5">
+        <f>1293-H22</f>
+        <v>664</v>
+      </c>
+      <c r="H22" s="5">
+        <v>629</v>
+      </c>
       <c r="L22" s="5">
         <v>1693</v>
       </c>
@@ -1929,6 +2086,20 @@
       <c r="B23" t="s">
         <v>68</v>
       </c>
+      <c r="C23" s="5">
+        <f>215-D23</f>
+        <v>117</v>
+      </c>
+      <c r="D23" s="5">
+        <v>98</v>
+      </c>
+      <c r="G23" s="5">
+        <f>553-H23</f>
+        <v>213</v>
+      </c>
+      <c r="H23" s="5">
+        <v>340</v>
+      </c>
       <c r="L23" s="5">
         <v>249</v>
       </c>
@@ -1943,6 +2114,20 @@
       <c r="B24" t="s">
         <v>69</v>
       </c>
+      <c r="C24" s="5">
+        <f>202-D24</f>
+        <v>-211</v>
+      </c>
+      <c r="D24" s="5">
+        <v>413</v>
+      </c>
+      <c r="G24" s="5">
+        <f>-1962-H24</f>
+        <v>-1876</v>
+      </c>
+      <c r="H24" s="5">
+        <v>-86</v>
+      </c>
       <c r="L24" s="5">
         <v>-42</v>
       </c>
@@ -1957,12 +2142,44 @@
       <c r="B25" t="s">
         <v>70</v>
       </c>
+      <c r="C25" s="5">
+        <f t="shared" ref="C25:J25" si="13">+C21-C22+C23+C24</f>
+        <v>-514</v>
+      </c>
+      <c r="D25" s="5">
+        <f t="shared" si="13"/>
+        <v>-870</v>
+      </c>
+      <c r="E25" s="5">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="F25" s="5">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="G25" s="5">
+        <f t="shared" si="13"/>
+        <v>-4270</v>
+      </c>
+      <c r="H25" s="5">
+        <f t="shared" si="13"/>
+        <v>-518</v>
+      </c>
+      <c r="I25" s="5">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="J25" s="5">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
       <c r="L25" s="5">
-        <f t="shared" ref="L25:M25" si="13">+L21-L22+L23+L24</f>
+        <f t="shared" ref="L25:M25" si="14">+L21-L22+L23+L24</f>
         <v>-4991</v>
       </c>
       <c r="M25" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>242</v>
       </c>
       <c r="N25" s="5">
@@ -1974,6 +2191,20 @@
       <c r="B26" t="s">
         <v>71</v>
       </c>
+      <c r="C26" s="5">
+        <f>152-D26</f>
+        <v>14</v>
+      </c>
+      <c r="D26" s="5">
+        <v>138</v>
+      </c>
+      <c r="G26" s="5">
+        <f>29-H26</f>
+        <v>6</v>
+      </c>
+      <c r="H26" s="5">
+        <v>23</v>
+      </c>
       <c r="L26" s="5">
         <v>-363</v>
       </c>
@@ -1988,12 +2219,44 @@
       <c r="B27" t="s">
         <v>72</v>
       </c>
+      <c r="C27" s="5">
+        <f t="shared" ref="C27:J27" si="15">+C25-C26</f>
+        <v>-528</v>
+      </c>
+      <c r="D27" s="5">
+        <f t="shared" si="15"/>
+        <v>-1008</v>
+      </c>
+      <c r="E27" s="5">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="F27" s="5">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="G27" s="5">
+        <f t="shared" si="15"/>
+        <v>-4276</v>
+      </c>
+      <c r="H27" s="5">
+        <f t="shared" si="15"/>
+        <v>-541</v>
+      </c>
+      <c r="I27" s="5">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="J27" s="5">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="L27" s="5">
-        <f t="shared" ref="L27:M27" si="14">+L25-L26</f>
+        <f t="shared" ref="L27:M27" si="16">+L25-L26</f>
         <v>-4628</v>
       </c>
       <c r="M27" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>791</v>
       </c>
       <c r="N27" s="5">
@@ -2005,16 +2268,40 @@
       <c r="B29" t="s">
         <v>73</v>
       </c>
+      <c r="C29" s="8">
+        <f t="shared" ref="C29:G29" si="17">+C27/C30</f>
+        <v>-0.18194348725017229</v>
+      </c>
+      <c r="D29" s="8">
+        <f t="shared" si="17"/>
+        <v>-0.34414475930351657</v>
+      </c>
+      <c r="E29" s="8" t="e">
+        <f t="shared" si="17"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F29" s="8" t="e">
+        <f t="shared" si="17"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G29" s="8">
+        <f t="shared" si="17"/>
+        <v>-0.87640910022545604</v>
+      </c>
+      <c r="H29" s="8">
+        <f>+H27/H30</f>
+        <v>-9.225784447476125E-2</v>
+      </c>
       <c r="K29" s="8" t="e">
-        <f t="shared" ref="K29:M29" si="15">+K27/K30</f>
+        <f t="shared" ref="K29:M29" si="18">+K27/K30</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L29" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>-1.6774193548387097</v>
       </c>
       <c r="M29" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>0.2777387640449438</v>
       </c>
       <c r="N29" s="8">
@@ -2026,6 +2313,18 @@
       <c r="B30" t="s">
         <v>19</v>
       </c>
+      <c r="C30" s="5">
+        <v>2902</v>
+      </c>
+      <c r="D30" s="5">
+        <v>2929</v>
+      </c>
+      <c r="G30" s="5">
+        <v>4879</v>
+      </c>
+      <c r="H30" s="5">
+        <v>5864</v>
+      </c>
       <c r="L30" s="5">
         <v>2759</v>
       </c>
@@ -2041,15 +2340,15 @@
         <v>74</v>
       </c>
       <c r="G32" s="11">
-        <f t="shared" ref="G32:G34" si="16">+G11/C11-1</f>
+        <f t="shared" ref="G32:G34" si="19">+G11/C11-1</f>
         <v>-0.284393063583815</v>
       </c>
       <c r="L32" s="9" t="e">
-        <f t="shared" ref="L32:M32" si="17">+L11/K11-1</f>
+        <f t="shared" ref="L32:M32" si="20">+L11/K11-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M32" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>6.7191453472027041E-2</v>
       </c>
       <c r="N32" s="9">
@@ -2062,19 +2361,19 @@
         <v>75</v>
       </c>
       <c r="G33" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0.315959595959596</v>
       </c>
       <c r="L33" s="9" t="e">
-        <f t="shared" ref="L33:N35" si="18">+L12/K12-1</f>
+        <f t="shared" ref="L33:N35" si="21">+L12/K12-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M33" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>0.96407340398035668</v>
       </c>
       <c r="N33" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>0.49848664297933931</v>
       </c>
     </row>
@@ -2083,19 +2382,19 @@
         <v>76</v>
       </c>
       <c r="G34" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>0.12517193947730409</v>
       </c>
       <c r="L34" s="9" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="M34" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>-0.11516379601485982</v>
       </c>
       <c r="N34" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>0.22175572519083975</v>
       </c>
     </row>
@@ -2116,15 +2415,15 @@
       <c r="J35" s="7"/>
       <c r="K35" s="7"/>
       <c r="L35" s="10" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="M35" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>0.34928275729276992</v>
       </c>
       <c r="N35" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>0.3324295397788084</v>
       </c>
     </row>
@@ -2133,43 +2432,43 @@
         <v>78</v>
       </c>
       <c r="C36" s="9">
-        <f t="shared" ref="C36:J36" si="19">+C16/C14</f>
-        <v>0</v>
-      </c>
-      <c r="D36" s="9" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="C36:J36" si="22">+C16/C14</f>
+        <v>0.51758052618637818</v>
+      </c>
+      <c r="D36" s="9">
+        <f t="shared" si="22"/>
+        <v>0.43944976664210267</v>
+      </c>
+      <c r="E36" s="9" t="e">
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="E36" s="9" t="e">
-        <f t="shared" si="19"/>
+      <c r="F36" s="9" t="e">
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F36" s="9" t="e">
-        <f t="shared" si="19"/>
+      <c r="G36" s="9">
+        <f t="shared" si="22"/>
+        <v>0.49126544524925436</v>
+      </c>
+      <c r="H36" s="9">
+        <f t="shared" si="22"/>
+        <v>0.55272587663168671</v>
+      </c>
+      <c r="I36" s="9" t="e">
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G36" s="9">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="H36" s="9" t="e">
-        <f t="shared" si="19"/>
+      <c r="J36" s="9" t="e">
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I36" s="9" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J36" s="9" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
-      </c>
       <c r="L36" s="9">
-        <f t="shared" ref="L36:M36" si="20">+L16/L14</f>
+        <f t="shared" ref="L36:M36" si="23">+L16/L14</f>
         <v>0.41176470588235292</v>
       </c>
       <c r="M36" s="9">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>0.4294684266856939</v>
       </c>
       <c r="N36" s="9">
@@ -2182,43 +2481,43 @@
         <v>79</v>
       </c>
       <c r="C37" s="9">
-        <f t="shared" ref="C37:J37" si="21">+C21/C14</f>
-        <v>0</v>
-      </c>
-      <c r="D37" s="9" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" ref="C37:J37" si="24">+C21/C14</f>
+        <v>6.6388000983525937E-3</v>
+      </c>
+      <c r="D37" s="9">
+        <f t="shared" si="24"/>
+        <v>-0.23827069516089414</v>
+      </c>
+      <c r="E37" s="9" t="e">
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="E37" s="9" t="e">
-        <f t="shared" si="21"/>
+      <c r="F37" s="9" t="e">
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F37" s="9" t="e">
-        <f t="shared" si="21"/>
+      <c r="G37" s="9">
+        <f t="shared" si="24"/>
+        <v>-0.41393268001704303</v>
+      </c>
+      <c r="H37" s="9">
+        <f t="shared" si="24"/>
+        <v>-1.8300486306629126E-2</v>
+      </c>
+      <c r="I37" s="9" t="e">
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G37" s="9">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="H37" s="9" t="e">
-        <f t="shared" si="21"/>
+      <c r="J37" s="9" t="e">
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I37" s="9" t="e">
-        <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J37" s="9" t="e">
-        <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
-      </c>
       <c r="L37" s="9">
-        <f t="shared" ref="L37:M37" si="22">+L21/L14</f>
+        <f t="shared" ref="L37:M37" si="25">+L21/L14</f>
         <v>-0.33744103205930492</v>
       </c>
       <c r="M37" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>3.325008919015341E-2</v>
       </c>
       <c r="N37" s="9">
@@ -2230,44 +2529,44 @@
       <c r="B38" t="s">
         <v>80</v>
       </c>
-      <c r="C38" s="9" t="e">
-        <f t="shared" ref="C38:J38" si="23">+C26/C25</f>
+      <c r="C38" s="9">
+        <f t="shared" ref="C38:J38" si="26">+C26/C25</f>
+        <v>-2.7237354085603113E-2</v>
+      </c>
+      <c r="D38" s="9">
+        <f t="shared" si="26"/>
+        <v>-0.15862068965517243</v>
+      </c>
+      <c r="E38" s="9" t="e">
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="D38" s="9" t="e">
-        <f t="shared" si="23"/>
+      <c r="F38" s="9" t="e">
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="E38" s="9" t="e">
-        <f t="shared" si="23"/>
+      <c r="G38" s="9">
+        <f t="shared" si="26"/>
+        <v>-1.405152224824356E-3</v>
+      </c>
+      <c r="H38" s="9">
+        <f t="shared" si="26"/>
+        <v>-4.4401544401544403E-2</v>
+      </c>
+      <c r="I38" s="9" t="e">
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F38" s="9" t="e">
-        <f t="shared" si="23"/>
+      <c r="J38" s="9" t="e">
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G38" s="9" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H38" s="9" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I38" s="9" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J38" s="9" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
       <c r="L38" s="9">
-        <f t="shared" ref="L38:M38" si="24">+L26/L25</f>
+        <f t="shared" ref="L38:M38" si="27">+L26/L25</f>
         <v>7.2730915648166694E-2</v>
       </c>
       <c r="M38" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>-2.2685950413223139</v>
       </c>
       <c r="N38" s="9">
@@ -2335,7 +2634,7 @@
         <v>86</v>
       </c>
       <c r="M45" s="5">
-        <f t="shared" ref="M45" si="25">+SUM(M40:M44)</f>
+        <f t="shared" ref="M45" si="28">+SUM(M40:M44)</f>
         <v>16108</v>
       </c>
       <c r="N45" s="5">
@@ -2425,7 +2724,7 @@
         <v>94</v>
       </c>
       <c r="M53" s="5">
-        <f t="shared" ref="M53" si="26">+SUM(M46:M52)</f>
+        <f t="shared" ref="M53" si="29">+SUM(M46:M52)</f>
         <v>40954</v>
       </c>
       <c r="N53" s="5">
@@ -2438,7 +2737,7 @@
         <v>95</v>
       </c>
       <c r="M54" s="7">
-        <f t="shared" ref="M54" si="27">+M53+M45</f>
+        <f t="shared" ref="M54" si="30">+M53+M45</f>
         <v>57062</v>
       </c>
       <c r="N54" s="7">
@@ -2603,11 +2902,11 @@
         <v>72</v>
       </c>
       <c r="L68" s="5">
-        <f t="shared" ref="L68:M68" si="28">+L27</f>
+        <f t="shared" ref="L68:M68" si="31">+L27</f>
         <v>-4628</v>
       </c>
       <c r="M68" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>791</v>
       </c>
       <c r="N68" s="5">
@@ -2791,11 +3090,11 @@
         <v>118</v>
       </c>
       <c r="L81" s="5">
-        <f t="shared" ref="L81:M81" si="29">+SUM(L74:L80)</f>
+        <f t="shared" ref="L81:M81" si="32">+SUM(L74:L80)</f>
         <v>2006</v>
       </c>
       <c r="M81" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1673</v>
       </c>
       <c r="N81" s="5">
@@ -2817,11 +3116,11 @@
       <c r="J82" s="7"/>
       <c r="K82" s="7"/>
       <c r="L82" s="7">
-        <f t="shared" ref="L82:M82" si="30">+L81+SUM(L68:L73)</f>
+        <f t="shared" ref="L82:M82" si="33">+L81+SUM(L68:L73)</f>
         <v>4520</v>
       </c>
       <c r="M82" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>5776</v>
       </c>
       <c r="N82" s="7">
@@ -2908,11 +3207,11 @@
         <v>120</v>
       </c>
       <c r="L88" s="7">
-        <f t="shared" ref="L88:M88" si="31">+SUM(L83:L87)</f>
+        <f t="shared" ref="L88:M88" si="34">+SUM(L83:L87)</f>
         <v>-4867</v>
       </c>
       <c r="M88" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>-10796</v>
       </c>
       <c r="N88" s="7">
@@ -3065,11 +3364,11 @@
         <v>134</v>
       </c>
       <c r="L98" s="5">
-        <f t="shared" ref="L98:M98" si="32">+L96+L88+L82+L97</f>
+        <f t="shared" ref="L98:M98" si="35">+L96+L88+L82+L97</f>
         <v>73</v>
       </c>
       <c r="M98" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>6811</v>
       </c>
       <c r="N98" s="5">
